--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -1,26 +1,449 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D600EC3A-E168-4CDB-B6CB-2D9151059E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="4" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Calculations" sheetId="3" r:id="rId3"/>
+    <sheet name="Sales Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Lists" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="132">
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>Dilusha</t>
+  </si>
+  <si>
+    <t>Sarath</t>
+  </si>
+  <si>
+    <t>Minol</t>
+  </si>
+  <si>
+    <t>Enul</t>
+  </si>
+  <si>
+    <t>Dasun</t>
+  </si>
+  <si>
+    <t>Senuri</t>
+  </si>
+  <si>
+    <t>Devid</t>
+  </si>
+  <si>
+    <t>Oshada</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Webcam</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Computers</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Debit Card</t>
+  </si>
+  <si>
+    <t>Bank Transfer</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>ABC Technologies</t>
+  </si>
+  <si>
+    <t>Global Solutions</t>
+  </si>
+  <si>
+    <t>Smart Education</t>
+  </si>
+  <si>
+    <t>Prime Holdings</t>
+  </si>
+  <si>
+    <t>Lanka Enterprises</t>
+  </si>
+  <si>
+    <t>TechWorld</t>
+  </si>
+  <si>
+    <t>Future Systems</t>
+  </si>
+  <si>
+    <t>Digital Lanka</t>
+  </si>
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>ORD001</t>
+  </si>
+  <si>
+    <t>ORD002</t>
+  </si>
+  <si>
+    <t>ORD003</t>
+  </si>
+  <si>
+    <t>ORD004</t>
+  </si>
+  <si>
+    <t>ORD005</t>
+  </si>
+  <si>
+    <t>ORD006</t>
+  </si>
+  <si>
+    <t>ORD007</t>
+  </si>
+  <si>
+    <t>ORD008</t>
+  </si>
+  <si>
+    <t>ORD009</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>ORD010</t>
+  </si>
+  <si>
+    <t>18/01/2026</t>
+  </si>
+  <si>
+    <t>ORD011</t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>ORD012</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>ORD013</t>
+  </si>
+  <si>
+    <t>25/01/2026</t>
+  </si>
+  <si>
+    <t>ORD014</t>
+  </si>
+  <si>
+    <t>28/01/2026</t>
+  </si>
+  <si>
+    <t>ORD015</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>ORD016</t>
+  </si>
+  <si>
+    <t>ORD017</t>
+  </si>
+  <si>
+    <t>ORD018</t>
+  </si>
+  <si>
+    <t>ORD019</t>
+  </si>
+  <si>
+    <t>ORD020</t>
+  </si>
+  <si>
+    <t>ORD021</t>
+  </si>
+  <si>
+    <t>ORD022</t>
+  </si>
+  <si>
+    <t>14/02/2026</t>
+  </si>
+  <si>
+    <t>ORD023</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>ORD024</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>ORD025</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>ORD026</t>
+  </si>
+  <si>
+    <t>22/02/2026</t>
+  </si>
+  <si>
+    <t>ORD027</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>ORD028</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>ORD029</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>ORD030</t>
+  </si>
+  <si>
+    <t>ORD031</t>
+  </si>
+  <si>
+    <t>ORD032</t>
+  </si>
+  <si>
+    <t>ORD033</t>
+  </si>
+  <si>
+    <t>ORD034</t>
+  </si>
+  <si>
+    <t>ORD035</t>
+  </si>
+  <si>
+    <t>ORD036</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
+  </si>
+  <si>
+    <t>ORD037</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>ORD038</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>ORD039</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>ORD040</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>ORD041</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>ORD042</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>ORD043</t>
+  </si>
+  <si>
+    <t>28/03/2026</t>
+  </si>
+  <si>
+    <t>ORD044</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>ORD045</t>
+  </si>
+  <si>
+    <t>ORD046</t>
+  </si>
+  <si>
+    <t>ORD047</t>
+  </si>
+  <si>
+    <t>ORD048</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>ORD049</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>ORD050</t>
+  </si>
+  <si>
+    <t>25/04/2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total Quantity Sold</t>
+  </si>
+  <si>
+    <t>Number of Orders</t>
+  </si>
+  <si>
+    <t>Average Order Value</t>
+  </si>
+  <si>
+    <t>Highest Sale</t>
+  </si>
+  <si>
+    <t>Lowest Sale</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +451,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,17 +496,425 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +925,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56EF8F25-73E6-4863-9BA8-DBE529445E76}" name="SalesTable" displayName="SalesTable" ref="A1:K51" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
+  <autoFilter ref="A1:K51" xr:uid="{56EF8F25-73E6-4863-9BA8-DBE529445E76}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{0FA6D7FC-4E67-4EA5-9546-6B6D0E9C6569}" name="Order ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{49C83AEB-0A78-434C-A5AF-129CB44E291A}" name="Date" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{77B6507D-4D2A-4056-8388-7FED18A23295}" name="Customer" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{AFD53509-289A-4831-855B-2A02B6D82CEA}" name="Region" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{76559D00-BEC6-4BD5-B7BA-2D231E10DCAF}" name="Salesperson" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{AA75DE1C-08E9-4A97-8CDF-8F4A1532ED73}" name="Product" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{7556264E-3B32-45DD-92F3-5F26126EFE14}" name="Category" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{196A2CEA-D321-4539-B8DA-6BB0190659C9}" name="Quantity" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{6639D84B-5F16-4FE4-87E1-AFE4A47433BE}" name="Unit Price" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{23D6942E-98A1-4E2B-915C-4D410E731B59}" name="Total Sales" dataDxfId="2">
+      <calculatedColumnFormula>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{F68FB0F3-2D52-4A36-BD6B-029D6BB71D3C}" name="Payment Method" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -85,7 +966,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -97,7 +978,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -144,6 +1025,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -179,6 +1077,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -330,10 +1245,2053 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E678CE-0F2F-4A54-9D61-992795E3777A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE9B18C-9F45-4B2D-B24C-4271EB14C90A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1D65C6-FEF1-4656-8613-EFBCAEDD2EBF}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="12">
+        <f>SUM(SalesTable[Total Sales])</f>
+        <v>45285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="13">
+        <f>SUM(SalesTable[Quantity])</f>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4">
+        <f>COUNTA(SalesTable[Order ID])</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5">
+        <f>AVEDEV(SalesTable[Total Sales])</f>
+        <v>485.89600000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6">
+        <f>MAX(SalesTable[Total Sales])</f>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7">
+        <f>MIN(SalesTable[Total Sales])</f>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36001277-4A17-4655-A0DA-497ED2E4F0D4}">
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="9">
+        <v>2</v>
+      </c>
+      <c r="I2" s="7">
+        <v>850</v>
+      </c>
+      <c r="J2" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1700</v>
+      </c>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="10">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8">
+        <v>320</v>
+      </c>
+      <c r="J3" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>960</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="9">
+        <v>5</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45</v>
+      </c>
+      <c r="J4" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>225</v>
+      </c>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="10">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>25</v>
+      </c>
+      <c r="J5" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>200</v>
+      </c>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="9">
+        <v>4</v>
+      </c>
+      <c r="I6" s="7">
+        <v>75</v>
+      </c>
+      <c r="J6" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>300</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="10">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8">
+        <v>280</v>
+      </c>
+      <c r="J7" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>560</v>
+      </c>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46296</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="9">
+        <v>6</v>
+      </c>
+      <c r="I8" s="7">
+        <v>65</v>
+      </c>
+      <c r="J8" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>390</v>
+      </c>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46357</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="10">
+        <v>3</v>
+      </c>
+      <c r="I9" s="8">
+        <v>450</v>
+      </c>
+      <c r="J9" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1350</v>
+      </c>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9">
+        <v>4</v>
+      </c>
+      <c r="I10" s="7">
+        <v>320</v>
+      </c>
+      <c r="J10" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1280</v>
+      </c>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>850</v>
+      </c>
+      <c r="J11" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>850</v>
+      </c>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="9">
+        <v>10</v>
+      </c>
+      <c r="I12" s="7">
+        <v>25</v>
+      </c>
+      <c r="J12" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>250</v>
+      </c>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="10">
+        <v>6</v>
+      </c>
+      <c r="I13" s="8">
+        <v>45</v>
+      </c>
+      <c r="J13" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>270</v>
+      </c>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="9">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>280</v>
+      </c>
+      <c r="J14" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>840</v>
+      </c>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="10">
+        <v>7</v>
+      </c>
+      <c r="I15" s="8">
+        <v>75</v>
+      </c>
+      <c r="J15" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>525</v>
+      </c>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="9">
+        <v>2</v>
+      </c>
+      <c r="I16" s="7">
+        <v>850</v>
+      </c>
+      <c r="J16" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1700</v>
+      </c>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46055</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="10">
+        <v>5</v>
+      </c>
+      <c r="I17" s="8">
+        <v>65</v>
+      </c>
+      <c r="J17" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>325</v>
+      </c>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="9">
+        <v>4</v>
+      </c>
+      <c r="I18" s="7">
+        <v>450</v>
+      </c>
+      <c r="J18" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1800</v>
+      </c>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46175</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="10">
+        <v>12</v>
+      </c>
+      <c r="I19" s="8">
+        <v>25</v>
+      </c>
+      <c r="J19" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>300</v>
+      </c>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46236</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="9">
+        <v>2</v>
+      </c>
+      <c r="I20" s="7">
+        <v>320</v>
+      </c>
+      <c r="J20" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>640</v>
+      </c>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46297</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="10">
+        <v>3</v>
+      </c>
+      <c r="I21" s="8">
+        <v>850</v>
+      </c>
+      <c r="J21" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>2550</v>
+      </c>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46358</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="9">
+        <v>8</v>
+      </c>
+      <c r="I22" s="7">
+        <v>45</v>
+      </c>
+      <c r="J22" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>360</v>
+      </c>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="10">
+        <v>2</v>
+      </c>
+      <c r="I23" s="8">
+        <v>280</v>
+      </c>
+      <c r="J23" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>560</v>
+      </c>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="9">
+        <v>5</v>
+      </c>
+      <c r="I24" s="7">
+        <v>75</v>
+      </c>
+      <c r="J24" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>375</v>
+      </c>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="10">
+        <v>2</v>
+      </c>
+      <c r="I25" s="8">
+        <v>450</v>
+      </c>
+      <c r="J25" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>900</v>
+      </c>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="9">
+        <v>7</v>
+      </c>
+      <c r="I26" s="7">
+        <v>65</v>
+      </c>
+      <c r="J26" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>455</v>
+      </c>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="10">
+        <v>2</v>
+      </c>
+      <c r="I27" s="8">
+        <v>850</v>
+      </c>
+      <c r="J27" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1700</v>
+      </c>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="9">
+        <v>15</v>
+      </c>
+      <c r="I28" s="7">
+        <v>25</v>
+      </c>
+      <c r="J28" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>375</v>
+      </c>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="10">
+        <v>3</v>
+      </c>
+      <c r="I29" s="8">
+        <v>320</v>
+      </c>
+      <c r="J29" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>960</v>
+      </c>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="9">
+        <v>6</v>
+      </c>
+      <c r="I30" s="7">
+        <v>75</v>
+      </c>
+      <c r="J30" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>450</v>
+      </c>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46056</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="10">
+        <v>3</v>
+      </c>
+      <c r="I31" s="8">
+        <v>450</v>
+      </c>
+      <c r="J31" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1350</v>
+      </c>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="9">
+        <v>4</v>
+      </c>
+      <c r="I32" s="7">
+        <v>280</v>
+      </c>
+      <c r="J32" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1120</v>
+      </c>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46176</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="10">
+        <v>2</v>
+      </c>
+      <c r="I33" s="8">
+        <v>850</v>
+      </c>
+      <c r="J33" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1700</v>
+      </c>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="9">
+        <v>10</v>
+      </c>
+      <c r="I34" s="7">
+        <v>45</v>
+      </c>
+      <c r="J34" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>450</v>
+      </c>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46298</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="10">
+        <v>8</v>
+      </c>
+      <c r="I35" s="8">
+        <v>65</v>
+      </c>
+      <c r="J35" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>520</v>
+      </c>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46359</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="9">
+        <v>4</v>
+      </c>
+      <c r="I36" s="7">
+        <v>320</v>
+      </c>
+      <c r="J36" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1280</v>
+      </c>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="10">
+        <v>20</v>
+      </c>
+      <c r="I37" s="8">
+        <v>25</v>
+      </c>
+      <c r="J37" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>500</v>
+      </c>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="9">
+        <v>2</v>
+      </c>
+      <c r="I38" s="7">
+        <v>450</v>
+      </c>
+      <c r="J38" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>900</v>
+      </c>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="10">
+        <v>9</v>
+      </c>
+      <c r="I39" s="8">
+        <v>75</v>
+      </c>
+      <c r="J39" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>675</v>
+      </c>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="9">
+        <v>1</v>
+      </c>
+      <c r="I40" s="7">
+        <v>850</v>
+      </c>
+      <c r="J40" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>850</v>
+      </c>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="10">
+        <v>3</v>
+      </c>
+      <c r="I41" s="8">
+        <v>280</v>
+      </c>
+      <c r="J41" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>840</v>
+      </c>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="9">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>450</v>
+      </c>
+      <c r="J42" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1350</v>
+      </c>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" s="10">
+        <v>12</v>
+      </c>
+      <c r="I43" s="8">
+        <v>45</v>
+      </c>
+      <c r="J43" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>540</v>
+      </c>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="9">
+        <v>2</v>
+      </c>
+      <c r="I44" s="7">
+        <v>850</v>
+      </c>
+      <c r="J44" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1700</v>
+      </c>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" s="10">
+        <v>10</v>
+      </c>
+      <c r="I45" s="8">
+        <v>65</v>
+      </c>
+      <c r="J45" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>650</v>
+      </c>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46026</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="9">
+        <v>5</v>
+      </c>
+      <c r="I46" s="7">
+        <v>320</v>
+      </c>
+      <c r="J46" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1600</v>
+      </c>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46146</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" s="10">
+        <v>18</v>
+      </c>
+      <c r="I47" s="8">
+        <v>25</v>
+      </c>
+      <c r="J47" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>450</v>
+      </c>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" s="9">
+        <v>4</v>
+      </c>
+      <c r="I48" s="7">
+        <v>450</v>
+      </c>
+      <c r="J48" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>1800</v>
+      </c>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="10">
+        <v>3</v>
+      </c>
+      <c r="I49" s="8">
+        <v>850</v>
+      </c>
+      <c r="J49" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>2550</v>
+      </c>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="9">
+        <v>2</v>
+      </c>
+      <c r="I50" s="7">
+        <v>280</v>
+      </c>
+      <c r="J50" s="7">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>560</v>
+      </c>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="10">
+        <v>10</v>
+      </c>
+      <c r="I51" s="8">
+        <v>75</v>
+      </c>
+      <c r="J51" s="8">
+        <f>SalesTable[[#This Row],[Quantity]]*SalesTable[[#This Row],[Unit Price]]</f>
+        <v>750</v>
+      </c>
+      <c r="K51" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J2:J51">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1514CF98-1168-426A-A01F-F692A5C04037}">
+          <x14:formula1>
+            <xm:f>Lists!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D51</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C86A5359-E68A-4C58-AA92-68F638A6AF92}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E51</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{323F6EDD-9FCB-4538-9939-769070BE6EE8}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F51</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{293A73D2-4BEE-4FEA-9E5F-ACFDE211DC51}">
+          <x14:formula1>
+            <xm:f>Lists!$E$2:$E$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K51</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF56CF7C-8CCB-4DC7-8227-C90F0F3EDC82}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D600EC3A-E168-4CDB-B6CB-2D9151059E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD19108-D6E8-4AF6-A488-C6CFA3FF5340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="4" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="133">
   <si>
     <t>Region</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>Lowest Sale</t>
+  </si>
+  <si>
+    <t>Sales</t>
   </si>
 </sst>
 </file>
@@ -1264,22 +1267,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1D65C6-FEF1-4656-8613-EFBCAEDD2EBF}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1287,8 +1296,15 @@
         <f>SUM(SalesTable[Total Sales])</f>
         <v>45285</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f>SUMIF(SalesTable[Region],D2,SalesTable[Total Sales])</f>
+        <v>12045</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -1296,8 +1312,15 @@
         <f>SUM(SalesTable[Quantity])</f>
         <v>277</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>SUMIF(SalesTable[Region],D3,SalesTable[Total Sales])</f>
+        <v>9740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -1305,8 +1328,15 @@
         <f>COUNTA(SalesTable[Order ID])</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f>SUMIF(SalesTable[Region],D4,SalesTable[Total Sales])</f>
+        <v>10705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -1314,8 +1344,15 @@
         <f>AVEDEV(SalesTable[Total Sales])</f>
         <v>485.89600000000007</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <f>SUMIF(SalesTable[Region],D5,SalesTable[Total Sales])</f>
+        <v>12795</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -1324,7 +1361,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD19108-D6E8-4AF6-A488-C6CFA3FF5340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD6C0A9-8532-4ED5-A28A-CCCF859B872F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="138">
   <si>
     <t>Region</t>
   </si>
@@ -437,6 +437,21 @@
   </si>
   <si>
     <t>Sales</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
   </si>
 </sst>
 </file>
@@ -1267,14 +1282,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1D65C6-FEF1-4656-8613-EFBCAEDD2EBF}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>125</v>
       </c>
@@ -1287,8 +1305,32 @@
       <c r="E1" s="11" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1303,8 +1345,36 @@
         <f>SUMIF(SalesTable[Region],D2,SalesTable[Total Sales])</f>
         <v>12045</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <f>SUMIF(SalesTable[Salesperson],G2,SalesTable[Total Sales])</f>
+        <v>7595</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(SalesTable[Product],J2,SalesTable[Total Sales])</f>
+        <v>15300</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
+        <f>SUMIF(SalesTable[Category],M2,SalesTable[Total Sales])</f>
+        <v>22020</v>
+      </c>
+      <c r="P2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q2">
+        <f>SUMIFS(SalesTable[Total Sales],SalesTable[Date],"&gt;="&amp;DATE(2026,1,1),SalesTable[Date],"&lt;"&amp;DATE(2026,2,1))</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -1319,8 +1389,36 @@
         <f>SUMIF(SalesTable[Region],D3,SalesTable[Total Sales])</f>
         <v>9740</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <f>SUMIF(SalesTable[Salesperson],G3,SalesTable[Total Sales])</f>
+        <v>5620</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <f>SUMIF(SalesTable[Product],J3,SalesTable[Total Sales])</f>
+        <v>6720</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <f>SUMIF(SalesTable[Category],M3,SalesTable[Total Sales])</f>
+        <v>6260</v>
+      </c>
+      <c r="P3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q3">
+        <f>SUMIFS(SalesTable[Total Sales],SalesTable[Date],"&gt;="&amp;DATE(2026,2,1),SalesTable[Date],"&lt;"&amp;DATE(2026,3,1))</f>
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -1335,8 +1433,36 @@
         <f>SUMIF(SalesTable[Region],D4,SalesTable[Total Sales])</f>
         <v>10705</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <f>SUMIF(SalesTable[Salesperson],G4,SalesTable[Total Sales])</f>
+        <v>4470</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <f>SUMIF(SalesTable[Product],J4,SalesTable[Total Sales])</f>
+        <v>1845</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <f>SUMIF(SalesTable[Category],M4,SalesTable[Total Sales])</f>
+        <v>3075</v>
+      </c>
+      <c r="P4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q4">
+        <f>SUMIFS(SalesTable[Total Sales],SalesTable[Date],"&gt;="&amp;DATE(2026,3,1),SalesTable[Date],"&lt;"&amp;DATE(2026,4,1))</f>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -1351,8 +1477,36 @@
         <f>SUMIF(SalesTable[Region],D5,SalesTable[Total Sales])</f>
         <v>12795</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <f>SUMIF(SalesTable[Salesperson],G5,SalesTable[Total Sales])</f>
+        <v>5130</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5">
+        <f>SUMIF(SalesTable[Product],J5,SalesTable[Total Sales])</f>
+        <v>2075</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <f>SUMIF(SalesTable[Category],M5,SalesTable[Total Sales])</f>
+        <v>4480</v>
+      </c>
+      <c r="P5" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q5">
+        <f>SUMIFS(SalesTable[Total Sales],SalesTable[Date],"&gt;="&amp;DATE(2026,4,1),SalesTable[Date],"&lt;"&amp;DATE(2026,5,1))</f>
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -1360,14 +1514,81 @@
         <f>MAX(SalesTable[Total Sales])</f>
         <v>2550</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <f>SUMIF(SalesTable[Salesperson],G6,SalesTable[Total Sales])</f>
+        <v>4450</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <f>SUMIF(SalesTable[Product],J6,SalesTable[Total Sales])</f>
+        <v>3075</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
+        <f>SUMIF(SalesTable[Category],M6,SalesTable[Total Sales])</f>
+        <v>9450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
       <c r="B7">
         <f>MIN(SalesTable[Total Sales])</f>
         <v>200</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <f>SUMIF(SalesTable[Salesperson],G7,SalesTable[Total Sales])</f>
+        <v>4120</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <f>SUMIF(SalesTable[Product],J7,SalesTable[Total Sales])</f>
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <f>SUMIF(SalesTable[Salesperson],G8,SalesTable[Total Sales])</f>
+        <v>6235</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8">
+        <f>SUMIF(SalesTable[Product],J8,SalesTable[Total Sales])</f>
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <f>SUMIF(SalesTable[Salesperson],G9,SalesTable[Total Sales])</f>
+        <v>7665</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9">
+        <f>SUMIF(SalesTable[Product],J9,SalesTable[Total Sales])</f>
+        <v>9450</v>
       </c>
     </row>
   </sheetData>

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD6C0A9-8532-4ED5-A28A-CCCF859B872F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42C9FCE-C870-4A6E-A763-65D47B26F5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="145">
   <si>
     <t>Region</t>
   </si>
@@ -452,6 +452,27 @@
   </si>
   <si>
     <t>April</t>
+  </si>
+  <si>
+    <t>Sales Performance Analysis</t>
+  </si>
+  <si>
+    <t>Sales by Region</t>
+  </si>
+  <si>
+    <t>Sales by Product</t>
+  </si>
+  <si>
+    <t>Total  Sales</t>
+  </si>
+  <si>
+    <t>Sales by Category</t>
+  </si>
+  <si>
+    <t>Salesperson Performance</t>
+  </si>
+  <si>
+    <t>Monthly Sales</t>
   </si>
 </sst>
 </file>
@@ -461,7 +482,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,6 +501,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -527,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -546,6 +575,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1273,9 +1303,307 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE9B18C-9F45-4B2D-B24C-4271EB14C90A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <f>Calculations!E2</f>
+        <v>12045</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <f>Calculations!N2</f>
+        <v>22020</v>
+      </c>
+      <c r="G5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5">
+        <f>Calculations!Q2</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>Calculations!E3</f>
+        <v>9740</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <f>Calculations!N3</f>
+        <v>6260</v>
+      </c>
+      <c r="G6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6">
+        <f>Calculations!Q3</f>
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <f>Calculations!E4</f>
+        <v>10705</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <f>Calculations!N4</f>
+        <v>3075</v>
+      </c>
+      <c r="G7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7">
+        <f>Calculations!Q4</f>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <f>Calculations!E5</f>
+        <v>12795</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <f>Calculations!N5</f>
+        <v>4480</v>
+      </c>
+      <c r="G8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8">
+        <f>Calculations!Q5</f>
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <f>Calculations!N6</f>
+        <v>9450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <f>Calculations!K2</f>
+        <v>15300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <f>Calculations!K3</f>
+        <v>6720</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <f>Calculations!H2</f>
+        <v>7595</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <f>Calculations!K4</f>
+        <v>1845</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <f>Calculations!H3</f>
+        <v>5620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <f>Calculations!K5</f>
+        <v>2075</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <f>Calculations!H4</f>
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <f>Calculations!K6</f>
+        <v>3075</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <f>Calculations!H5</f>
+        <v>5130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <f>Calculations!K7</f>
+        <v>4480</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <f>Calculations!H6</f>
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <f>Calculations!K8</f>
+        <v>2340</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18">
+        <f>Calculations!H7</f>
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <f>Calculations!K9</f>
+        <v>9450</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <f>Calculations!H8</f>
+        <v>6235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20">
+        <f>Calculations!H9</f>
+        <v>7665</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42C9FCE-C870-4A6E-A763-65D47B26F5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C9B659-8991-4BAC-99B1-B2431D537DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
@@ -975,6 +975,4572 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$5:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$5:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12045</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9740</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10705</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12795</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2D48-4934-BF01-C5EB0208FB67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2018497520"/>
+        <c:axId val="2021543760"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2018497520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2021543760"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2021543760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2018497520"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Product</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total  Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$12:$A$19</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Keyboard</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mouse</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Headphones</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Webcam</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$12:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>15300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6720</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2075</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3075</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4480</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2340</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E7C0-4589-B047-469FE5233A31}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="50174496"/>
+        <c:axId val="2021563920"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50174496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2021563920"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2021563920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50174496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Monthly Sales Trend</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$G$5:$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$H$5:$H$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2635</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2920</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3BD0-4778-936E-31DF62EBB800}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2019551200"/>
+        <c:axId val="42252176"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2019551200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="42252176"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="42252176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2019551200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$D$5:$D$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Computers</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Accessories</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Audio</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Office</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>22020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6260</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3075</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4480</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C974-4F1E-84C7-8D910FE791EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Salesperson Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$D$13:$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Dilusha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sarath</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minol</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Enul</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Dasun</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Senuri</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Devid</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Oshada</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$E$13:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>7595</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5620</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4470</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5130</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4450</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4120</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6235</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7665</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D7C-4825-97BB-BB002FF2DF56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="35152432"/>
+        <c:axId val="42236336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="35152432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="42236336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="42236336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35152432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1503</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>316464</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{725F24B5-F3A9-72DF-37F6-92C7AE0B4E3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>174811</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>283882</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>49306</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9C936C0-8A22-A883-2019-7D47133A89C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>14940</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>174810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>298823</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>49305</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{357A3666-066E-7572-4127-8F423BD41BE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>612587</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>8610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>329045</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>92430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E31182A-1098-F984-B7EC-17D67F9617A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>770</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>4167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>286836</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171844</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39D1519A-B75F-8C31-2FDD-5573375168CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56EF8F25-73E6-4863-9BA8-DBE529445E76}" name="SalesTable" displayName="SalesTable" ref="A1:K51" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A1:K51" xr:uid="{56EF8F25-73E6-4863-9BA8-DBE529445E76}"/>
@@ -1605,6 +6171,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C9B659-8991-4BAC-99B1-B2431D537DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A858F0-5451-4D69-A3C5-CB563AB47526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="153">
   <si>
     <t>Region</t>
   </si>
@@ -473,16 +473,41 @@
   </si>
   <si>
     <t>Monthly Sales</t>
+  </si>
+  <si>
+    <t>NOVA TECH SOLUTIONS</t>
+  </si>
+  <si>
+    <t>January - April 2026</t>
+  </si>
+  <si>
+    <t>SALES PERFORMANCE DASHBOARD</t>
+  </si>
+  <si>
+    <t>TOTAL SALES</t>
+  </si>
+  <si>
+    <t>TOTAL ORDERS</t>
+  </si>
+  <si>
+    <t>UNITS SOLD</t>
+  </si>
+  <si>
+    <t>AVG ORDER VALUE</t>
+  </si>
+  <si>
+    <t>HIGHEST SALE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="[$LKR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,6 +534,36 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -556,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -576,6 +631,29 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2058,6 +2136,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F013-40A8-AF93-3F8980E028CE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2073,6 +2156,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F013-40A8-AF93-3F8980E028CE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2088,6 +2176,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F013-40A8-AF93-3F8980E028CE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -2103,6 +2196,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-F013-40A8-AF93-3F8980E028CE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -2118,6 +2216,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-F013-40A8-AF93-3F8980E028CE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -5860,9 +5963,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E678CE-0F2F-4A54-9D61-992795E3777A}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:15" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B2" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+      <c r="B3" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="H6" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="K6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" s="23"/>
+      <c r="N6" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="19">
+        <f>Calculations!B2</f>
+        <v>45285</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="18">
+        <f>Calculations!B4</f>
+        <v>50</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="H7" s="22">
+        <f>Calculations!B3</f>
+        <v>277</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="K7" s="18">
+        <f>Calculations!B5</f>
+        <v>485.89600000000007</v>
+      </c>
+      <c r="L7" s="18"/>
+      <c r="N7" s="18">
+        <f>Calculations!B6</f>
+        <v>2550</v>
+      </c>
+      <c r="O7" s="18"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6184,6 +6399,7 @@
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
     <col min="14" max="14" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A858F0-5451-4D69-A3C5-CB563AB47526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F257A7AB-B2FA-460B-B60E-0F9CBA9B07DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
@@ -507,7 +507,7 @@
     <numFmt numFmtId="164" formatCode="[$LKR]\ #,##0.00;[Red][$LKR]\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$LKR]\ #,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,7 +563,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -590,7 +597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -607,11 +614,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -640,19 +688,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6000,67 +6051,67 @@
       <c r="H4" s="17"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="18" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="H6" s="18" t="s">
+      <c r="F6" s="23"/>
+      <c r="H6" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="K6" s="23" t="s">
+      <c r="I6" s="23"/>
+      <c r="K6" s="22" t="s">
         <v>151</v>
       </c>
       <c r="L6" s="23"/>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="18"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="19">
+      <c r="B7" s="24">
         <f>Calculations!B2</f>
         <v>45285</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="18">
+      <c r="C7" s="24"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="21">
         <f>Calculations!B4</f>
         <v>50</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="H7" s="22">
+      <c r="F7" s="21"/>
+      <c r="H7" s="21">
         <f>Calculations!B3</f>
         <v>277</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="K7" s="18">
+      <c r="I7" s="21"/>
+      <c r="K7" s="21">
         <f>Calculations!B5</f>
         <v>485.89600000000007</v>
       </c>
-      <c r="L7" s="18"/>
-      <c r="N7" s="18">
+      <c r="L7" s="21"/>
+      <c r="N7" s="21">
         <f>Calculations!B6</f>
         <v>2550</v>
       </c>
-      <c r="O7" s="18"/>
+      <c r="O7" s="21"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F257A7AB-B2FA-460B-B60E-0F9CBA9B07DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DE372-2A3C-4D86-B5DB-D24F9BB8F460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1139,6 +1139,2013 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>Monthly Sales Trend</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Calculations!$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Calculations!$P$2:$P$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Calculations!$Q$2:$Q$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2635</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2920</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-19C9-4C2A-A550-823EE7C51A49}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1073731263"/>
+        <c:axId val="1019689135"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1073731263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1019689135"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1019689135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1073731263"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Salesperson Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$E$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$D$13:$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Dilusha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sarath</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minol</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Enul</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Dasun</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Senuri</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Devid</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Oshada</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$E$13:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>7665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7595</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6235</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5620</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5130</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4470</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4450</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6D7C-4825-97BB-BB002FF2DF56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="35152432"/>
+        <c:axId val="42236336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="35152432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="42236336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="42236336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35152432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Calculations!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Calculations!$D$2:$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Calculations!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12045</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9740</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10705</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12795</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5664-4BA9-9D96-4E880FEE981E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1141875871"/>
+        <c:axId val="1019712175"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1141875871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1019712175"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1019712175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1141875871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Product</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Calculations!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Calculations!$J$2:$J$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Keyboard</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mouse</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Headphones</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Webcam</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Calculations!$K$2:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>15300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6720</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2075</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3075</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4480</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2340</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54AC-4956-A7AF-C37360A989DF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1245680351"/>
+        <c:axId val="1144773487"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1245680351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1144773487"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1144773487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1245680351"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Calculations!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-ABEA-4EED-B12F-93096BCCB33F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-ABEA-4EED-B12F-93096BCCB33F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-ABEA-4EED-B12F-93096BCCB33F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-ABEA-4EED-B12F-93096BCCB33F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-ABEA-4EED-B12F-93096BCCB33F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Calculations!$M$2:$M$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Computers</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Accessories</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Audio</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Office</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Calculations!$N$2:$N$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>22020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6260</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3075</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4480</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-ABEA-4EED-B12F-93096BCCB33F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Salesperson Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Calculations!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Calculations!$G$2:$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Oshada</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dilusha</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Devid</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sarath</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Enul</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Minol</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Dasun</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Senuri</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Calculations!$H$2:$H$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>7665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7595</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6235</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5620</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5130</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4470</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4450</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-877C-44E6-9C06-A65D970AC794}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1148117199"/>
+        <c:axId val="1144782607"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1148117199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1144782607"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1144782607"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1148117199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Sales by Region</a:t>
             </a:r>
           </a:p>
@@ -1423,7 +3430,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1765,7 +3772,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2085,7 +4092,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2421,350 +4428,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Salesperson Performance</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$E$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total Sales</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$D$13:$D$20</c:f>
-              <c:strCache>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>Dilusha</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sarath</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Minol</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Enul</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Dasun</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Senuri</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Devid</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Oshada</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$E$13:$E$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>7595</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5620</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4470</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5130</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4450</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4120</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6235</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7665</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6D7C-4825-97BB-BB002FF2DF56}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="35152432"/>
-        <c:axId val="42236336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="35152432"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="42236336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="42236336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="35152432"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2964,8 +4668,168 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3073,6 +4937,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3083,6 +4952,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3114,6 +4988,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3467,8 +5344,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3672,23 +5549,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3793,8 +5669,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3926,20 +5802,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3972,8 +5847,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4081,11 +5956,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -4096,11 +5966,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -4132,9 +5997,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4488,8 +6350,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4546,7 +6408,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -4597,13 +6459,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -4614,19 +6469,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4664,7 +6512,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -5007,8 +6855,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5065,7 +6913,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -5116,6 +6964,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5126,12 +6981,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -5169,6 +7031,511 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -5510,7 +7877,2245 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5860</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>20648</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD83F9EF-CE59-486E-B335-DAD62B31482C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>174172</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89BC6281-B0C3-489C-80A7-FA3FA1194FA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>606880</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>587830</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>170328</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1015737-876D-4912-BECF-3B1EC9C6F68E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>585106</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C657C0-BEF9-40BC-97F1-31657FAFC83F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>582623</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>5763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>8964</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F92F7F83-FA4B-46D2-BEBE-FF05DD33F386}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -6130,6 +10735,7 @@
     <mergeCell ref="B7:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6327,7 +10933,7 @@
       </c>
       <c r="E13">
         <f>Calculations!H2</f>
-        <v>7595</v>
+        <v>7665</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -6343,7 +10949,7 @@
       </c>
       <c r="E14">
         <f>Calculations!H3</f>
-        <v>5620</v>
+        <v>7595</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -6359,7 +10965,7 @@
       </c>
       <c r="E15">
         <f>Calculations!H4</f>
-        <v>4470</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -6375,7 +10981,7 @@
       </c>
       <c r="E16">
         <f>Calculations!H5</f>
-        <v>5130</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -6391,7 +10997,7 @@
       </c>
       <c r="E17">
         <f>Calculations!H6</f>
-        <v>4450</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -6407,7 +11013,7 @@
       </c>
       <c r="E18">
         <f>Calculations!H7</f>
-        <v>4120</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -6423,7 +11029,7 @@
       </c>
       <c r="E19">
         <f>Calculations!H8</f>
-        <v>6235</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -6432,7 +11038,7 @@
       </c>
       <c r="E20">
         <f>Calculations!H9</f>
-        <v>7665</v>
+        <v>4120</v>
       </c>
     </row>
   </sheetData>
@@ -6508,11 +11114,11 @@
         <v>12045</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <f>SUMIF(SalesTable[Salesperson],G2,SalesTable[Total Sales])</f>
-        <v>7595</v>
+        <v>7665</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -6552,11 +11158,11 @@
         <v>9740</v>
       </c>
       <c r="G3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <f>SUMIF(SalesTable[Salesperson],G3,SalesTable[Total Sales])</f>
-        <v>5620</v>
+        <v>7595</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
@@ -6596,11 +11202,11 @@
         <v>10705</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4">
         <f>SUMIF(SalesTable[Salesperson],G4,SalesTable[Total Sales])</f>
-        <v>4470</v>
+        <v>6235</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -6640,11 +11246,11 @@
         <v>12795</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <f>SUMIF(SalesTable[Salesperson],G5,SalesTable[Total Sales])</f>
-        <v>5130</v>
+        <v>5620</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -6677,11 +11283,11 @@
         <v>2550</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <f>SUMIF(SalesTable[Salesperson],G6,SalesTable[Total Sales])</f>
-        <v>4450</v>
+        <v>5130</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -6707,11 +11313,11 @@
         <v>200</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <f>SUMIF(SalesTable[Salesperson],G7,SalesTable[Total Sales])</f>
-        <v>4120</v>
+        <v>4470</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
@@ -6723,11 +11329,11 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="G8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <f>SUMIF(SalesTable[Salesperson],G8,SalesTable[Total Sales])</f>
-        <v>6235</v>
+        <v>4450</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -6739,11 +11345,11 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="G9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9">
         <f>SUMIF(SalesTable[Salesperson],G9,SalesTable[Total Sales])</f>
-        <v>7665</v>
+        <v>4120</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -6754,6 +11360,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:H9">
+    <sortCondition descending="1" ref="H2:H9"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Sales_Performance_Analysis.xlsx
+++ b/Sales_Performance_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BI-Projects\sales-performance-analysis-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DE372-2A3C-4D86-B5DB-D24F9BB8F460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9C8D39-68D7-42AF-BBC5-A47F17F5C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7497976-6BF0-42CC-AA8A-1BF9F284EB1D}"/>
   </bookViews>
@@ -1867,6 +1867,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Calculations!$D$2:$D$5</c:f>
@@ -1915,8 +1973,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
